--- a/request_forms/028_suggested_message_reply_form--request_forms.xlsx
+++ b/request_forms/028_suggested_message_reply_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'message_preferences_1',_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'message_preferences_1', 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'message_preferences_2',_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'message_preferences_2', 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'message_preferences_3',_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'message_preferences_3', 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'email',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'email', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'text',_'label':_'text'}</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'text', 'label': 'Text'}</t>
+          <t>Text</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'en',_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'en', 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_19,_'name':_'es',_'label':_'espanol'}</t>
+          <t>espanol</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 19, 'name': 'es', 'label': 'Espanol'}</t>
+          <t>Espanol</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'fr',_'label':_'francais'}</t>
+          <t>francais</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'fr', 'label': 'Francais'}</t>
+          <t>Francais</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
